--- a/테이블/테이블 양식.xlsx
+++ b/테이블/테이블 양식.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Unreal\Project TirgerGhostField\기획\테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D67EB6-C9B1-41E6-A71D-4359E5CB1194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEB0532-D89A-4B40-9B06-D365A03C6E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,7 +486,7 @@
       <formula1>"True, False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576" xr:uid="{F206F7A0-D8FF-4DF3-9E20-24D3E8262089}">
-      <formula1>"Integer, Float, String, Boolean, Enum, Struct, Class&lt;&gt;"</formula1>
+      <formula1>"Integer, Float, String, Bool, Enum, Struct, Class&lt;&gt;"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
